--- a/kofia.xlsx
+++ b/kofia.xlsx
@@ -552,40 +552,40 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.2602</v>
+        <v>3.26</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4842</v>
+        <v>3.484</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6316</v>
+        <v>3.631</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8476</v>
+        <v>3.847</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0732</v>
+        <v>4.073</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4702</v>
+        <v>4.47</v>
       </c>
       <c r="L2" t="n">
-        <v>4.6378</v>
+        <v>4.637</v>
       </c>
       <c r="M2" t="n">
-        <v>4.9254</v>
+        <v>4.925</v>
       </c>
       <c r="N2" t="n">
-        <v>5.1704</v>
+        <v>5.17</v>
       </c>
       <c r="O2" t="n">
-        <v>5.3842</v>
+        <v>5.384</v>
       </c>
       <c r="P2" t="n">
-        <v>5.5586</v>
+        <v>5.558</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.1954</v>
+        <v>6.195</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -625,40 +625,40 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.2844</v>
+        <v>4.284</v>
       </c>
       <c r="G3" t="n">
         <v>4.689</v>
       </c>
       <c r="H3" t="n">
-        <v>4.869400000000001</v>
+        <v>4.869</v>
       </c>
       <c r="I3" t="n">
-        <v>5.0876</v>
+        <v>5.087</v>
       </c>
       <c r="J3" t="n">
-        <v>5.3224</v>
+        <v>5.322</v>
       </c>
       <c r="K3" t="n">
-        <v>5.7864</v>
+        <v>5.786</v>
       </c>
       <c r="L3" t="n">
-        <v>6.0244</v>
+        <v>6.024</v>
       </c>
       <c r="M3" t="n">
-        <v>6.342000000000001</v>
+        <v>6.342</v>
       </c>
       <c r="N3" t="n">
-        <v>6.5306</v>
+        <v>6.53</v>
       </c>
       <c r="O3" t="n">
-        <v>6.6938</v>
+        <v>6.693</v>
       </c>
       <c r="P3" t="n">
-        <v>6.7368</v>
+        <v>6.736</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.263800000000001</v>
+        <v>7.263</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -707,31 +707,31 @@
         <v>4.278</v>
       </c>
       <c r="I4" t="n">
-        <v>4.525799999999999</v>
+        <v>4.525</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7674</v>
+        <v>4.767</v>
       </c>
       <c r="K4" t="n">
-        <v>5.2256</v>
+        <v>5.225</v>
       </c>
       <c r="L4" t="n">
-        <v>5.393800000000001</v>
+        <v>5.393</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6998</v>
+        <v>5.699</v>
       </c>
       <c r="N4" t="n">
-        <v>5.8588</v>
+        <v>5.858</v>
       </c>
       <c r="O4" t="n">
         <v>6.046</v>
       </c>
       <c r="P4" t="n">
-        <v>6.0866</v>
+        <v>6.086</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.6166</v>
+        <v>6.616</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -771,40 +771,40 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.9702</v>
+        <v>2.97</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0348</v>
+        <v>3.034</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1348</v>
+        <v>3.134</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4198</v>
+        <v>3.419</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6428</v>
+        <v>3.642</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8978</v>
+        <v>3.897</v>
       </c>
       <c r="L5" t="n">
-        <v>3.9098</v>
+        <v>3.909</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0034</v>
+        <v>4.003</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9736</v>
+        <v>3.973</v>
       </c>
       <c r="O5" t="n">
-        <v>3.976999999999999</v>
+        <v>3.976</v>
       </c>
       <c r="P5" t="n">
-        <v>4.228400000000001</v>
+        <v>4.228</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.1076</v>
+        <v>5.107</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -844,40 +844,40 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.0104</v>
+        <v>3.01</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0874</v>
+        <v>3.087</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2038</v>
+        <v>3.203</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4938</v>
+        <v>3.493</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7278</v>
+        <v>3.727</v>
       </c>
       <c r="K6" t="n">
-        <v>4.0006</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>4.0232</v>
+        <v>4.023</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1508</v>
+        <v>4.15</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1434</v>
+        <v>4.143</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2522</v>
+        <v>4.252</v>
       </c>
       <c r="P6" t="n">
-        <v>4.660600000000001</v>
+        <v>4.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.5036</v>
+        <v>5.503</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -917,40 +917,40 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.9906</v>
+        <v>2.99</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0534</v>
+        <v>3.053</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1506</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="n">
         <v>3.435</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6682</v>
+        <v>3.668</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9234</v>
+        <v>3.923</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9348</v>
+        <v>3.934</v>
       </c>
       <c r="M7" t="n">
-        <v>4.061400000000001</v>
+        <v>4.061</v>
       </c>
       <c r="N7" t="n">
-        <v>4.034000000000001</v>
+        <v>4.034</v>
       </c>
       <c r="O7" t="n">
         <v>4.152</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4444</v>
+        <v>4.444</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.2714</v>
+        <v>5.271</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -990,40 +990,40 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.3936</v>
+        <v>5.393</v>
       </c>
       <c r="G8" t="n">
-        <v>5.9866</v>
+        <v>5.986</v>
       </c>
       <c r="H8" t="n">
-        <v>6.3188</v>
+        <v>6.318</v>
       </c>
       <c r="I8" t="n">
         <v>6.606</v>
       </c>
       <c r="J8" t="n">
-        <v>6.9054</v>
+        <v>6.905</v>
       </c>
       <c r="K8" t="n">
-        <v>7.651000000000001</v>
+        <v>7.651</v>
       </c>
       <c r="L8" t="n">
-        <v>7.9788</v>
+        <v>7.978</v>
       </c>
       <c r="M8" t="n">
-        <v>8.325399999999998</v>
+        <v>8.324999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>8.4514</v>
+        <v>8.451000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>8.7006</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="P8" t="n">
         <v>8.842000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.572399999999998</v>
+        <v>9.571999999999999</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1066,49 +1066,49 @@
         <v>2.618</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7214</v>
+        <v>2.721</v>
       </c>
       <c r="H9" t="n">
         <v>2.827</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9974</v>
+        <v>2.997</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1402</v>
+        <v>3.14</v>
       </c>
       <c r="K9" t="n">
-        <v>3.337000000000001</v>
+        <v>3.337</v>
       </c>
       <c r="L9" t="n">
-        <v>3.3808</v>
+        <v>3.38</v>
       </c>
       <c r="M9" t="n">
-        <v>3.430000000000001</v>
+        <v>3.43</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5694</v>
+        <v>3.569</v>
       </c>
       <c r="O9" t="n">
         <v>3.592</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6562</v>
+        <v>3.656</v>
       </c>
       <c r="Q9" t="n">
         <v>3.725</v>
       </c>
       <c r="R9" t="n">
-        <v>3.7326</v>
+        <v>3.732</v>
       </c>
       <c r="S9" t="n">
         <v>3.687</v>
       </c>
       <c r="T9" t="n">
-        <v>3.6112</v>
+        <v>3.611</v>
       </c>
       <c r="U9" t="n">
-        <v>3.5158</v>
+        <v>3.515</v>
       </c>
     </row>
     <row r="10">
@@ -1136,34 +1136,34 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6306</v>
+        <v>2.63</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7522</v>
+        <v>2.752</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8386</v>
+        <v>2.838</v>
       </c>
       <c r="I10" t="n">
-        <v>3.0068</v>
+        <v>3.006</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1668</v>
+        <v>3.166</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3614</v>
+        <v>3.361</v>
       </c>
       <c r="L10" t="n">
-        <v>3.4212</v>
+        <v>3.421</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5298</v>
+        <v>3.529</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5762</v>
+        <v>3.576</v>
       </c>
       <c r="O10" t="n">
-        <v>3.775799999999999</v>
+        <v>3.775</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1209,40 +1209,40 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.4458</v>
+        <v>2.445</v>
       </c>
       <c r="G11" t="n">
         <v>2.56</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6602</v>
+        <v>2.66</v>
       </c>
       <c r="I11" t="n">
-        <v>2.8088</v>
+        <v>2.808</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9608</v>
+        <v>2.96</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1496</v>
+        <v>3.149</v>
       </c>
       <c r="L11" t="n">
         <v>3.215</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3342</v>
+        <v>3.334</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3868</v>
+        <v>3.386</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5426</v>
+        <v>3.542</v>
       </c>
       <c r="P11" t="n">
-        <v>3.5932</v>
+        <v>3.593</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.928199999999999</v>
+        <v>3.928</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1282,46 +1282,46 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.2286</v>
+        <v>3.228</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3884</v>
+        <v>3.388</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5028</v>
+        <v>3.502</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7378</v>
+        <v>3.737</v>
       </c>
       <c r="J12" t="n">
-        <v>4.0648</v>
+        <v>4.064</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2738</v>
+        <v>4.273</v>
       </c>
       <c r="L12" t="n">
-        <v>4.3222</v>
+        <v>4.322</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4434</v>
+        <v>4.443</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4462</v>
+        <v>4.446</v>
       </c>
       <c r="O12" t="n">
-        <v>4.597</v>
+        <v>4.596</v>
       </c>
       <c r="P12" t="n">
-        <v>4.686199999999999</v>
+        <v>4.686</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.0558</v>
+        <v>5.055</v>
       </c>
       <c r="R12" t="n">
-        <v>5.2298</v>
+        <v>5.229</v>
       </c>
       <c r="S12" t="n">
-        <v>5.398000000000001</v>
+        <v>5.398</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1355,46 +1355,46 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9822</v>
+        <v>2.982</v>
       </c>
       <c r="G13" t="n">
-        <v>3.0786</v>
+        <v>3.078</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1702</v>
+        <v>3.17</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3856</v>
+        <v>3.385</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7016</v>
+        <v>3.701</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9072</v>
+        <v>3.907</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9616</v>
+        <v>3.961</v>
       </c>
       <c r="M13" t="n">
-        <v>4.0708</v>
+        <v>4.07</v>
       </c>
       <c r="N13" t="n">
-        <v>4.0744</v>
+        <v>4.074</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2234</v>
+        <v>4.223</v>
       </c>
       <c r="P13" t="n">
-        <v>4.2776</v>
+        <v>4.277</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5764</v>
+        <v>4.576</v>
       </c>
       <c r="R13" t="n">
         <v>4.778</v>
       </c>
       <c r="S13" t="n">
-        <v>4.960800000000001</v>
+        <v>4.96</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1431,43 +1431,43 @@
         <v>2.8</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8852</v>
+        <v>2.885</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9734</v>
+        <v>2.973</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1686</v>
+        <v>3.168</v>
       </c>
       <c r="J14" t="n">
         <v>3.441</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5952</v>
+        <v>3.595</v>
       </c>
       <c r="L14" t="n">
-        <v>3.6336</v>
+        <v>3.633</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7556</v>
+        <v>3.755</v>
       </c>
       <c r="N14" t="n">
-        <v>3.7556</v>
+        <v>3.755</v>
       </c>
       <c r="O14" t="n">
-        <v>3.8784</v>
+        <v>3.878</v>
       </c>
       <c r="P14" t="n">
-        <v>3.9126</v>
+        <v>3.912</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.1656</v>
+        <v>4.165</v>
       </c>
       <c r="R14" t="n">
         <v>4.293</v>
       </c>
       <c r="S14" t="n">
-        <v>4.412999999999999</v>
+        <v>4.412</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -1501,46 +1501,46 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.7786</v>
+        <v>2.778</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8594</v>
+        <v>2.859</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9422</v>
+        <v>2.942</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1196</v>
+        <v>3.119</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3774</v>
+        <v>3.377</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5494</v>
+        <v>3.549</v>
       </c>
       <c r="L15" t="n">
-        <v>3.5676</v>
+        <v>3.567</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6678</v>
+        <v>3.667</v>
       </c>
       <c r="N15" t="n">
         <v>3.659</v>
       </c>
       <c r="O15" t="n">
-        <v>3.8012</v>
+        <v>3.801</v>
       </c>
       <c r="P15" t="n">
-        <v>3.8088</v>
+        <v>3.808</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.0702</v>
+        <v>4.07</v>
       </c>
       <c r="R15" t="n">
-        <v>4.1892</v>
+        <v>4.189</v>
       </c>
       <c r="S15" t="n">
-        <v>4.3088</v>
+        <v>4.308</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -1574,46 +1574,46 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.7786</v>
+        <v>2.778</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8594</v>
+        <v>2.859</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9422</v>
+        <v>2.942</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1196</v>
+        <v>3.119</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3774</v>
+        <v>3.377</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5494</v>
+        <v>3.549</v>
       </c>
       <c r="L16" t="n">
-        <v>3.5676</v>
+        <v>3.567</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6678</v>
+        <v>3.667</v>
       </c>
       <c r="N16" t="n">
         <v>3.662</v>
       </c>
       <c r="O16" t="n">
-        <v>3.8078</v>
+        <v>3.807</v>
       </c>
       <c r="P16" t="n">
-        <v>3.8322</v>
+        <v>3.832</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.0974</v>
+        <v>4.097</v>
       </c>
       <c r="R16" t="n">
-        <v>4.2172</v>
+        <v>4.217</v>
       </c>
       <c r="S16" t="n">
-        <v>4.3376</v>
+        <v>4.337</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1647,34 +1647,34 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.6922</v>
+        <v>2.692</v>
       </c>
       <c r="G17" t="n">
         <v>2.844</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9318</v>
+        <v>2.931</v>
       </c>
       <c r="I17" t="n">
-        <v>3.0902</v>
+        <v>3.09</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2356</v>
+        <v>3.235</v>
       </c>
       <c r="K17" t="n">
-        <v>3.4364</v>
+        <v>3.436</v>
       </c>
       <c r="L17" t="n">
-        <v>3.4982</v>
+        <v>3.498</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6506</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>3.678199999999999</v>
+        <v>3.678</v>
       </c>
       <c r="O17" t="n">
-        <v>3.8108</v>
+        <v>3.81</v>
       </c>
       <c r="P17" t="n">
         <v>3.875</v>
@@ -1720,34 +1720,34 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.6932</v>
+        <v>2.693</v>
       </c>
       <c r="G18" t="n">
-        <v>2.845</v>
+        <v>2.844</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9322</v>
+        <v>2.932</v>
       </c>
       <c r="I18" t="n">
-        <v>3.0898</v>
+        <v>3.089</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2356</v>
+        <v>3.235</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4378</v>
+        <v>3.437</v>
       </c>
       <c r="L18" t="n">
-        <v>3.4978</v>
+        <v>3.497</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6506</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>3.6772</v>
+        <v>3.677</v>
       </c>
       <c r="O18" t="n">
-        <v>3.8092</v>
+        <v>3.809</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1793,46 +1793,46 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.7892</v>
+        <v>2.789</v>
       </c>
       <c r="G19" t="n">
-        <v>2.8762</v>
+        <v>2.876</v>
       </c>
       <c r="H19" t="n">
-        <v>2.9634</v>
+        <v>2.963</v>
       </c>
       <c r="I19" t="n">
         <v>3.153</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4244</v>
+        <v>3.424</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5928</v>
+        <v>3.592</v>
       </c>
       <c r="L19" t="n">
-        <v>3.6308</v>
+        <v>3.63</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7432</v>
+        <v>3.743</v>
       </c>
       <c r="N19" t="n">
-        <v>3.7438</v>
+        <v>3.743</v>
       </c>
       <c r="O19" t="n">
-        <v>3.8566</v>
+        <v>3.856</v>
       </c>
       <c r="P19" t="n">
         <v>3.875</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.1162</v>
+        <v>4.116</v>
       </c>
       <c r="R19" t="n">
         <v>4.243</v>
       </c>
       <c r="S19" t="n">
-        <v>4.3524</v>
+        <v>4.352</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -1869,25 +1869,25 @@
         <v>2.573</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6578</v>
+        <v>2.657</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7368</v>
+        <v>2.736</v>
       </c>
       <c r="I20" t="n">
-        <v>2.9404</v>
+        <v>2.94</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2118</v>
+        <v>3.211</v>
       </c>
       <c r="K20" t="n">
-        <v>3.3688</v>
+        <v>3.368</v>
       </c>
       <c r="L20" t="n">
         <v>3.385</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4758</v>
+        <v>3.475</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1939,46 +1939,46 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.8822</v>
+        <v>2.882</v>
       </c>
       <c r="G21" t="n">
-        <v>2.9754</v>
+        <v>2.975</v>
       </c>
       <c r="H21" t="n">
-        <v>3.1098</v>
+        <v>3.109</v>
       </c>
       <c r="I21" t="n">
-        <v>3.3006</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5548</v>
+        <v>3.554</v>
       </c>
       <c r="K21" t="n">
-        <v>3.8298</v>
+        <v>3.829</v>
       </c>
       <c r="L21" t="n">
-        <v>3.8994</v>
+        <v>3.899</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9976</v>
+        <v>3.997</v>
       </c>
       <c r="N21" t="n">
-        <v>4.0036</v>
+        <v>4.003</v>
       </c>
       <c r="O21" t="n">
-        <v>4.0914</v>
+        <v>4.091</v>
       </c>
       <c r="P21" t="n">
-        <v>4.1442</v>
+        <v>4.144</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2726</v>
+        <v>4.272</v>
       </c>
       <c r="R21" t="n">
-        <v>4.2914</v>
+        <v>4.291</v>
       </c>
       <c r="S21" t="n">
-        <v>4.314400000000001</v>
+        <v>4.314</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2015,34 +2015,34 @@
         <v>2.83</v>
       </c>
       <c r="G22" t="n">
-        <v>2.9224</v>
+        <v>2.922</v>
       </c>
       <c r="H22" t="n">
         <v>3.044</v>
       </c>
       <c r="I22" t="n">
-        <v>3.2188</v>
+        <v>3.218</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4392</v>
+        <v>3.439</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7104</v>
+        <v>3.71</v>
       </c>
       <c r="L22" t="n">
-        <v>3.7684</v>
+        <v>3.768</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8692</v>
+        <v>3.869</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8762</v>
+        <v>3.876</v>
       </c>
       <c r="O22" t="n">
-        <v>3.9602</v>
+        <v>3.96</v>
       </c>
       <c r="P22" t="n">
-        <v>4.0064</v>
+        <v>4.006</v>
       </c>
       <c r="Q22" t="n">
         <v>4.131</v>
@@ -2051,7 +2051,7 @@
         <v>4.136</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1564</v>
+        <v>4.156</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2085,49 +2085,49 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.7824</v>
+        <v>2.782</v>
       </c>
       <c r="G23" t="n">
-        <v>2.8762</v>
+        <v>2.876</v>
       </c>
       <c r="H23" t="n">
-        <v>2.9828</v>
+        <v>2.982</v>
       </c>
       <c r="I23" t="n">
-        <v>3.1716</v>
+        <v>3.171</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3856</v>
+        <v>3.385</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6294</v>
+        <v>3.629</v>
       </c>
       <c r="L23" t="n">
-        <v>3.6796</v>
+        <v>3.679</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7722</v>
+        <v>3.772</v>
       </c>
       <c r="N23" t="n">
-        <v>3.7714</v>
+        <v>3.771</v>
       </c>
       <c r="O23" t="n">
-        <v>3.8346</v>
+        <v>3.834</v>
       </c>
       <c r="P23" t="n">
-        <v>3.8668</v>
+        <v>3.866</v>
       </c>
       <c r="Q23" t="n">
         <v>3.941</v>
       </c>
       <c r="R23" t="n">
-        <v>3.9188</v>
+        <v>3.918</v>
       </c>
       <c r="S23" t="n">
-        <v>3.9106</v>
+        <v>3.91</v>
       </c>
       <c r="T23" t="n">
-        <v>3.8234</v>
+        <v>3.823</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2161,43 +2161,43 @@
         <v>2.713</v>
       </c>
       <c r="G24" t="n">
-        <v>2.7918</v>
+        <v>2.791</v>
       </c>
       <c r="H24" t="n">
-        <v>2.8838</v>
+        <v>2.883</v>
       </c>
       <c r="I24" t="n">
-        <v>3.0818</v>
+        <v>3.081</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2862</v>
+        <v>3.286</v>
       </c>
       <c r="K24" t="n">
-        <v>3.5172</v>
+        <v>3.517</v>
       </c>
       <c r="L24" t="n">
         <v>3.552</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6294</v>
+        <v>3.629</v>
       </c>
       <c r="N24" t="n">
-        <v>3.6428</v>
+        <v>3.642</v>
       </c>
       <c r="O24" t="n">
-        <v>3.7854</v>
+        <v>3.785</v>
       </c>
       <c r="P24" t="n">
-        <v>3.8046</v>
+        <v>3.804</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.8618</v>
+        <v>3.861</v>
       </c>
       <c r="R24" t="n">
-        <v>3.8388</v>
+        <v>3.838</v>
       </c>
       <c r="S24" t="n">
-        <v>3.8262</v>
+        <v>3.826</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -2231,49 +2231,49 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.7756</v>
+        <v>2.775</v>
       </c>
       <c r="G25" t="n">
-        <v>2.8752</v>
+        <v>2.875</v>
       </c>
       <c r="H25" t="n">
-        <v>2.986</v>
+        <v>2.985</v>
       </c>
       <c r="I25" t="n">
-        <v>3.1794</v>
+        <v>3.179</v>
       </c>
       <c r="J25" t="n">
         <v>3.401</v>
       </c>
       <c r="K25" t="n">
-        <v>3.6586</v>
+        <v>3.658</v>
       </c>
       <c r="L25" t="n">
-        <v>3.708</v>
+        <v>3.707</v>
       </c>
       <c r="M25" t="n">
-        <v>3.801</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>3.7982</v>
+        <v>3.798</v>
       </c>
       <c r="O25" t="n">
-        <v>3.8632</v>
+        <v>3.863</v>
       </c>
       <c r="P25" t="n">
-        <v>3.8898</v>
+        <v>3.889</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.9736</v>
+        <v>3.973</v>
       </c>
       <c r="R25" t="n">
-        <v>3.9424</v>
+        <v>3.942</v>
       </c>
       <c r="S25" t="n">
-        <v>3.9338</v>
+        <v>3.933</v>
       </c>
       <c r="T25" t="n">
-        <v>3.8414</v>
+        <v>3.841</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2304,34 +2304,34 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.0906</v>
+        <v>3.09</v>
       </c>
       <c r="G26" t="n">
-        <v>3.236</v>
+        <v>3.235</v>
       </c>
       <c r="H26" t="n">
-        <v>3.4248</v>
+        <v>3.424</v>
       </c>
       <c r="I26" t="n">
-        <v>3.7006</v>
+        <v>3.7</v>
       </c>
       <c r="J26" t="n">
-        <v>4.0422</v>
+        <v>4.042</v>
       </c>
       <c r="K26" t="n">
-        <v>4.4292</v>
+        <v>4.429</v>
       </c>
       <c r="L26" t="n">
-        <v>4.5202</v>
+        <v>4.52</v>
       </c>
       <c r="M26" t="n">
-        <v>4.700200000000001</v>
+        <v>4.7</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4.9226</v>
+        <v>4.922</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.8876</v>
+        <v>2.887</v>
       </c>
       <c r="G27" t="n">
-        <v>2.97</v>
+        <v>2.969</v>
       </c>
       <c r="H27" t="n">
         <v>3.068</v>
@@ -2389,22 +2389,22 @@
         <v>3.286</v>
       </c>
       <c r="J27" t="n">
-        <v>3.550400000000001</v>
+        <v>3.55</v>
       </c>
       <c r="K27" t="n">
         <v>3.76</v>
       </c>
       <c r="L27" t="n">
-        <v>3.8038</v>
+        <v>3.803</v>
       </c>
       <c r="M27" t="n">
-        <v>3.919</v>
+        <v>3.918</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.0212</v>
+        <v>4.021</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2450,28 +2450,28 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.9862</v>
+        <v>2.986</v>
       </c>
       <c r="G28" t="n">
-        <v>3.0744</v>
+        <v>3.074</v>
       </c>
       <c r="H28" t="n">
-        <v>3.1914</v>
+        <v>3.191</v>
       </c>
       <c r="I28" t="n">
-        <v>3.4224</v>
+        <v>3.422</v>
       </c>
       <c r="J28" t="n">
-        <v>3.7242</v>
+        <v>3.724</v>
       </c>
       <c r="K28" t="n">
-        <v>3.9524</v>
+        <v>3.952</v>
       </c>
       <c r="L28" t="n">
-        <v>4.0074</v>
+        <v>4.007</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1314</v>
+        <v>4.131</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2523,34 +2523,34 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.8466</v>
+        <v>2.846</v>
       </c>
       <c r="G29" t="n">
-        <v>2.9304</v>
+        <v>2.93</v>
       </c>
       <c r="H29" t="n">
-        <v>3.0138</v>
+        <v>3.013</v>
       </c>
       <c r="I29" t="n">
         <v>3.219</v>
       </c>
       <c r="J29" t="n">
-        <v>3.4632</v>
+        <v>3.463</v>
       </c>
       <c r="K29" t="n">
-        <v>3.6572</v>
+        <v>3.657</v>
       </c>
       <c r="L29" t="n">
         <v>3.688</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7802</v>
+        <v>3.78</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.8796</v>
+        <v>3.879</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -2602,25 +2602,25 @@
         <v>3.191</v>
       </c>
       <c r="H30" t="n">
-        <v>3.3458</v>
+        <v>3.345</v>
       </c>
       <c r="I30" t="n">
-        <v>3.6198</v>
+        <v>3.619</v>
       </c>
       <c r="J30" t="n">
-        <v>3.9044</v>
+        <v>3.904</v>
       </c>
       <c r="K30" t="n">
-        <v>4.2232</v>
+        <v>4.223</v>
       </c>
       <c r="L30" t="n">
-        <v>4.2914</v>
+        <v>4.291</v>
       </c>
       <c r="M30" t="n">
-        <v>4.4586</v>
+        <v>4.458</v>
       </c>
       <c r="N30" t="n">
-        <v>4.5976</v>
+        <v>4.597</v>
       </c>
       <c r="O30" t="n">
         <v>4.883</v>
@@ -2629,7 +2629,7 @@
         <v>5.042</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.7988</v>
+        <v>5.798</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2672,37 +2672,37 @@
         <v>3.435</v>
       </c>
       <c r="G31" t="n">
-        <v>3.5516</v>
+        <v>3.551</v>
       </c>
       <c r="H31" t="n">
-        <v>3.7582</v>
+        <v>3.758</v>
       </c>
       <c r="I31" t="n">
-        <v>4.0472</v>
+        <v>4.047</v>
       </c>
       <c r="J31" t="n">
-        <v>4.3926</v>
+        <v>4.392</v>
       </c>
       <c r="K31" t="n">
-        <v>4.7554</v>
+        <v>4.755</v>
       </c>
       <c r="L31" t="n">
         <v>4.901</v>
       </c>
       <c r="M31" t="n">
-        <v>5.187600000000001</v>
+        <v>5.187</v>
       </c>
       <c r="N31" t="n">
         <v>5.454</v>
       </c>
       <c r="O31" t="n">
-        <v>5.9112</v>
+        <v>5.911</v>
       </c>
       <c r="P31" t="n">
         <v>6.026</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.7722</v>
+        <v>6.772</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -2742,37 +2742,37 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.2066</v>
+        <v>3.206</v>
       </c>
       <c r="G32" t="n">
-        <v>3.3074</v>
+        <v>3.307</v>
       </c>
       <c r="H32" t="n">
-        <v>3.4886</v>
+        <v>3.488</v>
       </c>
       <c r="I32" t="n">
-        <v>3.778799999999999</v>
+        <v>3.778</v>
       </c>
       <c r="J32" t="n">
-        <v>4.0814</v>
+        <v>4.081</v>
       </c>
       <c r="K32" t="n">
-        <v>4.4084</v>
+        <v>4.408</v>
       </c>
       <c r="L32" t="n">
-        <v>4.4936</v>
+        <v>4.493</v>
       </c>
       <c r="M32" t="n">
-        <v>4.7306</v>
+        <v>4.73</v>
       </c>
       <c r="N32" t="n">
-        <v>4.9572</v>
+        <v>4.957</v>
       </c>
       <c r="O32" t="n">
-        <v>5.3234</v>
+        <v>5.323</v>
       </c>
       <c r="P32" t="n">
-        <v>5.4976</v>
+        <v>5.497</v>
       </c>
       <c r="Q32" t="n">
         <v>6.26</v>
@@ -2815,40 +2815,40 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.9968</v>
+        <v>2.996</v>
       </c>
       <c r="G33" t="n">
-        <v>3.0758</v>
+        <v>3.075</v>
       </c>
       <c r="H33" t="n">
-        <v>3.1718</v>
+        <v>3.171</v>
       </c>
       <c r="I33" t="n">
-        <v>3.4086</v>
+        <v>3.408</v>
       </c>
       <c r="J33" t="n">
-        <v>3.6156</v>
+        <v>3.615</v>
       </c>
       <c r="K33" t="n">
-        <v>3.865</v>
+        <v>3.864</v>
       </c>
       <c r="L33" t="n">
-        <v>3.8948</v>
+        <v>3.894</v>
       </c>
       <c r="M33" t="n">
-        <v>3.9886</v>
+        <v>3.988</v>
       </c>
       <c r="N33" t="n">
-        <v>3.9758</v>
+        <v>3.975</v>
       </c>
       <c r="O33" t="n">
-        <v>4.0328</v>
+        <v>4.032</v>
       </c>
       <c r="P33" t="n">
-        <v>4.0674</v>
+        <v>4.067</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.5156</v>
+        <v>4.515</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -2888,40 +2888,40 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.0558</v>
+        <v>3.055</v>
       </c>
       <c r="G34" t="n">
         <v>3.128</v>
       </c>
       <c r="H34" t="n">
-        <v>3.2316</v>
+        <v>3.231</v>
       </c>
       <c r="I34" t="n">
-        <v>3.4768</v>
+        <v>3.476</v>
       </c>
       <c r="J34" t="n">
-        <v>3.6872</v>
+        <v>3.687</v>
       </c>
       <c r="K34" t="n">
-        <v>3.9418</v>
+        <v>3.941</v>
       </c>
       <c r="L34" t="n">
         <v>3.974</v>
       </c>
       <c r="M34" t="n">
-        <v>4.0784</v>
+        <v>4.078</v>
       </c>
       <c r="N34" t="n">
-        <v>4.0814</v>
+        <v>4.081</v>
       </c>
       <c r="O34" t="n">
         <v>4.201</v>
       </c>
       <c r="P34" t="n">
-        <v>4.361800000000001</v>
+        <v>4.361</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.2166</v>
+        <v>5.216</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -2961,28 +2961,28 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.0304</v>
+        <v>3.03</v>
       </c>
       <c r="G35" t="n">
-        <v>3.1018</v>
+        <v>3.101</v>
       </c>
       <c r="H35" t="n">
-        <v>3.1988</v>
+        <v>3.198</v>
       </c>
       <c r="I35" t="n">
-        <v>3.4434</v>
+        <v>3.443</v>
       </c>
       <c r="J35" t="n">
-        <v>3.6546</v>
+        <v>3.654</v>
       </c>
       <c r="K35" t="n">
-        <v>3.8962</v>
+        <v>3.896</v>
       </c>
       <c r="L35" t="n">
-        <v>3.9288</v>
+        <v>3.928</v>
       </c>
       <c r="M35" t="n">
-        <v>4.0252</v>
+        <v>4.025</v>
       </c>
       <c r="N35" t="n">
         <v>4.017</v>
@@ -2991,10 +2991,10 @@
         <v>4.099</v>
       </c>
       <c r="P35" t="n">
-        <v>4.1644</v>
+        <v>4.164</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.8522</v>
+        <v>4.852</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3034,22 +3034,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.9408</v>
+        <v>2.94</v>
       </c>
       <c r="G36" t="n">
-        <v>3.0208</v>
+        <v>3.02</v>
       </c>
       <c r="H36" t="n">
-        <v>3.1008</v>
+        <v>3.1</v>
       </c>
       <c r="I36" t="n">
-        <v>3.3386</v>
+        <v>3.338</v>
       </c>
       <c r="J36" t="n">
-        <v>3.5526</v>
+        <v>3.552</v>
       </c>
       <c r="K36" t="n">
-        <v>3.7864</v>
+        <v>3.786</v>
       </c>
       <c r="L36" t="n">
         <v>3.817</v>
@@ -3058,16 +3058,16 @@
         <v>3.889</v>
       </c>
       <c r="N36" t="n">
-        <v>3.8828</v>
+        <v>3.882</v>
       </c>
       <c r="O36" t="n">
-        <v>3.9432</v>
+        <v>3.943</v>
       </c>
       <c r="P36" t="n">
-        <v>3.9662</v>
+        <v>3.966</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.2326</v>
+        <v>4.232</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -3110,37 +3110,37 @@
         <v>3.78</v>
       </c>
       <c r="G37" t="n">
-        <v>4.2468</v>
+        <v>4.246</v>
       </c>
       <c r="H37" t="n">
-        <v>4.7354</v>
+        <v>4.735</v>
       </c>
       <c r="I37" t="n">
-        <v>5.119400000000001</v>
+        <v>5.119</v>
       </c>
       <c r="J37" t="n">
-        <v>5.8834</v>
+        <v>5.883</v>
       </c>
       <c r="K37" t="n">
-        <v>6.791200000000001</v>
+        <v>6.791</v>
       </c>
       <c r="L37" t="n">
-        <v>7.0982</v>
+        <v>7.098</v>
       </c>
       <c r="M37" t="n">
-        <v>7.460599999999999</v>
+        <v>7.46</v>
       </c>
       <c r="N37" t="n">
-        <v>7.606199999999999</v>
+        <v>7.606</v>
       </c>
       <c r="O37" t="n">
-        <v>7.7944</v>
+        <v>7.794</v>
       </c>
       <c r="P37" t="n">
-        <v>7.8256</v>
+        <v>7.825</v>
       </c>
       <c r="Q37" t="n">
-        <v>8.2636</v>
+        <v>8.263</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -3180,40 +3180,40 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4.8356</v>
+        <v>4.835</v>
       </c>
       <c r="G38" t="n">
-        <v>5.5568</v>
+        <v>5.556</v>
       </c>
       <c r="H38" t="n">
-        <v>6.2594</v>
+        <v>6.259</v>
       </c>
       <c r="I38" t="n">
-        <v>6.7994</v>
+        <v>6.799</v>
       </c>
       <c r="J38" t="n">
-        <v>7.823600000000001</v>
+        <v>7.823</v>
       </c>
       <c r="K38" t="n">
         <v>8.906000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>9.373999999999999</v>
+        <v>9.372999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>9.867799999999999</v>
+        <v>9.867000000000001</v>
       </c>
       <c r="N38" t="n">
         <v>10.024</v>
       </c>
       <c r="O38" t="n">
-        <v>10.1936</v>
+        <v>10.193</v>
       </c>
       <c r="P38" t="n">
-        <v>10.2238</v>
+        <v>10.223</v>
       </c>
       <c r="Q38" t="n">
-        <v>10.7152</v>
+        <v>10.715</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3253,40 +3253,40 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4.1568</v>
+        <v>4.156</v>
       </c>
       <c r="G39" t="n">
-        <v>4.7548</v>
+        <v>4.754</v>
       </c>
       <c r="H39" t="n">
-        <v>5.3242</v>
+        <v>5.324</v>
       </c>
       <c r="I39" t="n">
-        <v>5.8034</v>
+        <v>5.803</v>
       </c>
       <c r="J39" t="n">
-        <v>6.6958</v>
+        <v>6.695</v>
       </c>
       <c r="K39" t="n">
-        <v>7.7396</v>
+        <v>7.739</v>
       </c>
       <c r="L39" t="n">
-        <v>8.1326</v>
+        <v>8.132</v>
       </c>
       <c r="M39" t="n">
-        <v>8.5054</v>
+        <v>8.505000000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>8.6518</v>
+        <v>8.651</v>
       </c>
       <c r="O39" t="n">
         <v>8.843999999999999</v>
       </c>
       <c r="P39" t="n">
-        <v>8.879000000000001</v>
+        <v>8.879</v>
       </c>
       <c r="Q39" t="n">
-        <v>9.3596</v>
+        <v>9.359</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -3326,16 +3326,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3.3016</v>
+        <v>3.301</v>
       </c>
       <c r="G40" t="n">
-        <v>3.43</v>
+        <v>3.429</v>
       </c>
       <c r="H40" t="n">
-        <v>3.6058</v>
+        <v>3.605</v>
       </c>
       <c r="I40" t="n">
-        <v>3.8946</v>
+        <v>3.894</v>
       </c>
       <c r="J40" t="n">
         <v>4.197</v>
@@ -3344,19 +3344,19 @@
         <v>4.528</v>
       </c>
       <c r="L40" t="n">
-        <v>4.615399999999999</v>
+        <v>4.615</v>
       </c>
       <c r="M40" t="n">
-        <v>4.7996</v>
+        <v>4.799</v>
       </c>
       <c r="N40" t="n">
-        <v>4.9554</v>
+        <v>4.955</v>
       </c>
       <c r="O40" t="n">
-        <v>5.2622</v>
+        <v>5.262</v>
       </c>
       <c r="P40" t="n">
-        <v>5.4622</v>
+        <v>5.462</v>
       </c>
       <c r="Q40" t="n">
         <v>6.25</v>
@@ -3399,37 +3399,37 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3.6852</v>
+        <v>3.685</v>
       </c>
       <c r="G41" t="n">
-        <v>3.8542</v>
+        <v>3.854</v>
       </c>
       <c r="H41" t="n">
-        <v>4.0886</v>
+        <v>4.088</v>
       </c>
       <c r="I41" t="n">
-        <v>4.396199999999999</v>
+        <v>4.396</v>
       </c>
       <c r="J41" t="n">
-        <v>4.7488</v>
+        <v>4.748</v>
       </c>
       <c r="K41" t="n">
-        <v>5.127599999999999</v>
+        <v>5.127</v>
       </c>
       <c r="L41" t="n">
-        <v>5.290999999999999</v>
+        <v>5.29</v>
       </c>
       <c r="M41" t="n">
         <v>5.601</v>
       </c>
       <c r="N41" t="n">
-        <v>5.883599999999999</v>
+        <v>5.883</v>
       </c>
       <c r="O41" t="n">
-        <v>6.3686</v>
+        <v>6.368</v>
       </c>
       <c r="P41" t="n">
-        <v>6.5184</v>
+        <v>6.518</v>
       </c>
       <c r="Q41" t="n">
         <v>7.297</v>
@@ -3472,40 +3472,40 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3.422</v>
+        <v>3.421</v>
       </c>
       <c r="G42" t="n">
         <v>3.578</v>
       </c>
       <c r="H42" t="n">
-        <v>3.7806</v>
+        <v>3.78</v>
       </c>
       <c r="I42" t="n">
         <v>4.083</v>
       </c>
       <c r="J42" t="n">
-        <v>4.3982</v>
+        <v>4.398</v>
       </c>
       <c r="K42" t="n">
-        <v>4.749000000000001</v>
+        <v>4.749</v>
       </c>
       <c r="L42" t="n">
-        <v>4.849600000000001</v>
+        <v>4.849</v>
       </c>
       <c r="M42" t="n">
-        <v>5.1064</v>
+        <v>5.106</v>
       </c>
       <c r="N42" t="n">
-        <v>5.3686</v>
+        <v>5.368</v>
       </c>
       <c r="O42" t="n">
-        <v>5.7478</v>
+        <v>5.747</v>
       </c>
       <c r="P42" t="n">
         <v>5.961</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.7624</v>
+        <v>6.762</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -3545,40 +3545,40 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3.1448</v>
+        <v>3.144</v>
       </c>
       <c r="G43" t="n">
-        <v>3.2574</v>
+        <v>3.257</v>
       </c>
       <c r="H43" t="n">
-        <v>3.3708</v>
+        <v>3.37</v>
       </c>
       <c r="I43" t="n">
-        <v>3.6182</v>
+        <v>3.618</v>
       </c>
       <c r="J43" t="n">
-        <v>3.8428</v>
+        <v>3.842</v>
       </c>
       <c r="K43" t="n">
-        <v>4.0964</v>
+        <v>4.096</v>
       </c>
       <c r="L43" t="n">
         <v>4.136</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2416</v>
+        <v>4.241</v>
       </c>
       <c r="N43" t="n">
-        <v>4.2454</v>
+        <v>4.245</v>
       </c>
       <c r="O43" t="n">
-        <v>4.3454</v>
+        <v>4.345</v>
       </c>
       <c r="P43" t="n">
         <v>4.433</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.1258</v>
+        <v>5.125</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3618,40 +3618,40 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3.0188</v>
+        <v>3.018</v>
       </c>
       <c r="G44" t="n">
         <v>3.13</v>
       </c>
       <c r="H44" t="n">
-        <v>3.2252</v>
+        <v>3.225</v>
       </c>
       <c r="I44" t="n">
-        <v>3.4666</v>
+        <v>3.466</v>
       </c>
       <c r="J44" t="n">
-        <v>3.6942</v>
+        <v>3.694</v>
       </c>
       <c r="K44" t="n">
-        <v>3.9368</v>
+        <v>3.936</v>
       </c>
       <c r="L44" t="n">
-        <v>3.9772</v>
+        <v>3.977</v>
       </c>
       <c r="M44" t="n">
-        <v>4.0578</v>
+        <v>4.057</v>
       </c>
       <c r="N44" t="n">
-        <v>4.0644</v>
+        <v>4.064</v>
       </c>
       <c r="O44" t="n">
-        <v>4.1416</v>
+        <v>4.141</v>
       </c>
       <c r="P44" t="n">
-        <v>4.1972</v>
+        <v>4.197</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.4964</v>
+        <v>4.496</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
